--- a/nr-uniformisation-descriptions/ig/StructureDefinition-fr-core-practitioner.xlsx
+++ b/nr-uniformisation-descriptions/ig/StructureDefinition-fr-core-practitioner.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-11T10:38:49+00:00</t>
+    <t>2025-02-11T11:03:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-uniformisation-descriptions/ig/StructureDefinition-fr-core-practitioner.xlsx
+++ b/nr-uniformisation-descriptions/ig/StructureDefinition-fr-core-practitioner.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-11T11:03:37+00:00</t>
+    <t>2025-02-11T12:08:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -640,8 +640,7 @@
     <t>FR Core Practitioner Specialty Extension</t>
   </si>
   <si>
-    <t>This extension adds the element "specialty" to the FHIR Practitioner resource.
-http://esante.gouv.fr/sites/NOS/TABS/TRE_R38-SpecialiteOrdinale.tabs</t>
+    <t>This extension adds the element "specialty" to the FHIR Practitioner resource.</t>
   </si>
   <si>
     <t xml:space="preserve">ele-1

--- a/nr-uniformisation-descriptions/ig/StructureDefinition-fr-core-practitioner.xlsx
+++ b/nr-uniformisation-descriptions/ig/StructureDefinition-fr-core-practitioner.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-11T12:08:53+00:00</t>
+    <t>2025-02-11T15:31:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-uniformisation-descriptions/ig/StructureDefinition-fr-core-practitioner.xlsx
+++ b/nr-uniformisation-descriptions/ig/StructureDefinition-fr-core-practitioner.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-11T15:31:42+00:00</t>
+    <t>2025-02-11T17:07:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-uniformisation-descriptions/ig/StructureDefinition-fr-core-practitioner.xlsx
+++ b/nr-uniformisation-descriptions/ig/StructureDefinition-fr-core-practitioner.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-11T17:07:06+00:00</t>
+    <t>2025-02-11T17:08:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-uniformisation-descriptions/ig/StructureDefinition-fr-core-practitioner.xlsx
+++ b/nr-uniformisation-descriptions/ig/StructureDefinition-fr-core-practitioner.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-11T17:08:15+00:00</t>
+    <t>2025-02-11T17:29:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
